--- a/ig/test-tabs-svs/ValueSet-jdv-j374-autorite.xlsx
+++ b/ig/test-tabs-svs/ValueSet-jdv-j374-autorite.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="198">
   <si>
     <t>Property</t>
   </si>
@@ -128,7 +128,7 @@
     <t>used-codesystem</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r396-autorite|20260330120000</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r396-autorite|20260629120000</t>
   </si>
   <si>
     <t>version</t>
@@ -369,6 +369,192 @@
   </si>
   <si>
     <t>AT-975 : ATS de Saint-Pierre-Et-Miquelon</t>
+  </si>
+  <si>
+    <t>CD-01</t>
+  </si>
+  <si>
+    <t>CD-01 : Conseil départemental de l'Ain</t>
+  </si>
+  <si>
+    <t>CD-02</t>
+  </si>
+  <si>
+    <t>CD-02 : Conseil départemental del'Aisne</t>
+  </si>
+  <si>
+    <t>CD-03</t>
+  </si>
+  <si>
+    <t>CD-03 : Conseil départemental de l'Allier</t>
+  </si>
+  <si>
+    <t>CD-15</t>
+  </si>
+  <si>
+    <t>CD-15 : Conseil départemental du Cantal</t>
+  </si>
+  <si>
+    <t>CD-54</t>
+  </si>
+  <si>
+    <t>CD-54 : Conseil départemental de Meurthe et Moselle</t>
+  </si>
+  <si>
+    <t>CD-58</t>
+  </si>
+  <si>
+    <t>CD-58 : Conseil départemental de la Nièvre</t>
+  </si>
+  <si>
+    <t>CD-94</t>
+  </si>
+  <si>
+    <t>CD-94 : Conseil départemental du Val de Marne</t>
+  </si>
+  <si>
+    <t>CD-95</t>
+  </si>
+  <si>
+    <t>CD-95 : Conseil départemental du Val d'Oise</t>
+  </si>
+  <si>
+    <t>DDETS-01</t>
+  </si>
+  <si>
+    <t>DDETS-01 : Direction départementale de l'emploi, du travail et des solidarités Ain</t>
+  </si>
+  <si>
+    <t>DDETS-02</t>
+  </si>
+  <si>
+    <t>DDETS-02 : Direction départementale de l'emploi, du travail et des solidarités Aisne</t>
+  </si>
+  <si>
+    <t>DDETS-03</t>
+  </si>
+  <si>
+    <t>DDETS-03 : Direction départementale de l'emploi, du travail et des solidarités Allier</t>
+  </si>
+  <si>
+    <t>DDETS-95</t>
+  </si>
+  <si>
+    <t>DDETS-95 :Direction départementale de l'emploi, du travail et des solidarités Val d'Oise</t>
+  </si>
+  <si>
+    <t>DREETS-01</t>
+  </si>
+  <si>
+    <t>DREETS-01 : Direction de l'économie de l'emploi du travail et des solidarités Guadeloupe</t>
+  </si>
+  <si>
+    <t>DREETS-02</t>
+  </si>
+  <si>
+    <t>DREETS-02 :  Direction de l'économie de l'emploi du travail et des solidarités Martinique</t>
+  </si>
+  <si>
+    <t>DREETS-03</t>
+  </si>
+  <si>
+    <t>DREETS-03 :  Direction générale cohésion et population Guyane</t>
+  </si>
+  <si>
+    <t>DREETS-05</t>
+  </si>
+  <si>
+    <t>DREETS-05 :  Direction de l'économie de l'emploi du travail et des solidarités de La Réunion</t>
+  </si>
+  <si>
+    <t>DREETS-06</t>
+  </si>
+  <si>
+    <t>DREETS-06 : Direction de l'économie de l'emploi du travail et des solidarités Mayotte</t>
+  </si>
+  <si>
+    <t>DREETS-11</t>
+  </si>
+  <si>
+    <t>DREETS-11 : Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités d'Ile de France</t>
+  </si>
+  <si>
+    <t>DREETS-24</t>
+  </si>
+  <si>
+    <t>DREETS-24 :  Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Centre-Val de Loire</t>
+  </si>
+  <si>
+    <t>DREETS-27</t>
+  </si>
+  <si>
+    <t>DREETS-27 :  Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Bourgogne-Franche-Comté</t>
+  </si>
+  <si>
+    <t>DREETS-28</t>
+  </si>
+  <si>
+    <t>DREETS-28 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Normandie</t>
+  </si>
+  <si>
+    <t>DREETS-32</t>
+  </si>
+  <si>
+    <t>DREETS-32 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Hauts-de-France</t>
+  </si>
+  <si>
+    <t>DREETS-44</t>
+  </si>
+  <si>
+    <t>DREETS-44 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Grand Est</t>
+  </si>
+  <si>
+    <t>DREETS-52</t>
+  </si>
+  <si>
+    <t>DREETS-52 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Pays de la Loire</t>
+  </si>
+  <si>
+    <t>DREETS-53</t>
+  </si>
+  <si>
+    <t>DREETS-53 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Bretagne</t>
+  </si>
+  <si>
+    <t>DREETS-75</t>
+  </si>
+  <si>
+    <t>DREETS-75 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Nouvelle-Aquitaine</t>
+  </si>
+  <si>
+    <t>DREETS-76</t>
+  </si>
+  <si>
+    <t>DREETS-76 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Occitanie</t>
+  </si>
+  <si>
+    <t>DREETS-84</t>
+  </si>
+  <si>
+    <t>DREETS-84 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Auvergne-Rhône-Alpes</t>
+  </si>
+  <si>
+    <t>DREETS-93</t>
+  </si>
+  <si>
+    <t>DREETS-93 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Provence-Alpes-Côte d'Azur</t>
+  </si>
+  <si>
+    <t>DREETS-94</t>
+  </si>
+  <si>
+    <t>DREETS-94 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités de Corse</t>
+  </si>
+  <si>
+    <t>DRHIL-11</t>
+  </si>
+  <si>
+    <t>DRHIL-11 : Direction régionale et interdépartementale de l'Hébergement et du Logement Ile de France</t>
   </si>
   <si>
     <t>ENREG</t>
@@ -772,7 +958,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1743,6 +1929,657 @@
         <v>15</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="E47" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="F47" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="E48" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="F48" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="E49" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="F49" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="E50" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="F50" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="E51" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="F51" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="E52" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="F52" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="E53" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="F53" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="E54" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="F54" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="E55" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="F55" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="E56" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="F56" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="E57" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="F57" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="E58" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="F58" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="E59" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="F59" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="E60" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="F60" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="E61" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="F61" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="E62" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="F62" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="E63" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="F63" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="E64" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="F64" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="E65" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="F65" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="E66" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="F66" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="E67" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="F67" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="E68" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="F68" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E69" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="F69" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="E70" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="F70" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="E71" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="F71" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="E72" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="F72" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="E73" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="F73" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="E74" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="F74" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="E75" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="F75" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="E76" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="F76" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="E77" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="F77" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
